--- a/data/clean/price_table.xlsx
+++ b/data/clean/price_table.xlsx
@@ -11,6 +11,7 @@
     <sheet name="paid_price" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="substitutes_removed" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="long_data" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="control_data" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,12 +453,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Harris Teeter</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Whole Foods</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>n_stores</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>control_price</t>
         </is>
       </c>
     </row>
@@ -486,7 +497,13 @@
         <v>9.99</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>9.99</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10.49</v>
       </c>
     </row>
     <row r="3">
@@ -503,9 +520,15 @@
       <c r="F3" t="n">
         <v>2.79</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>2</v>
+      <c r="G3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.79</v>
       </c>
     </row>
     <row r="4">
@@ -520,11 +543,15 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>12.99</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13.99</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +568,15 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
         <v>13.49</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>11.99</v>
       </c>
     </row>
     <row r="6">
@@ -565,10 +596,16 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="H6" t="n">
         <v>19.49</v>
       </c>
-      <c r="H6" t="n">
-        <v>4</v>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16.99</v>
       </c>
     </row>
     <row r="7">
@@ -589,9 +626,11 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -611,9 +650,11 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -628,9 +669,11 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -645,9 +688,11 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -662,9 +707,11 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -684,9 +731,11 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -708,8 +757,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
         <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="14">
@@ -727,8 +780,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
         <v>2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="15">
@@ -744,9 +801,11 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
@@ -757,14 +816,22 @@
       <c r="C16" t="n">
         <v>3.99</v>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>2.29</v>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H16" t="n">
         <v>1.66</v>
       </c>
-      <c r="H16" t="n">
-        <v>2</v>
+      <c r="I16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.23</v>
       </c>
     </row>
     <row r="17">
@@ -776,14 +843,22 @@
       <c r="C17" t="n">
         <v>2.99</v>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>2.29</v>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H17" t="n">
         <v>1.66</v>
       </c>
-      <c r="H17" t="n">
-        <v>2</v>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.79</v>
       </c>
     </row>
     <row r="18">
@@ -801,8 +876,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="n">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
         <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.37</v>
       </c>
     </row>
     <row r="19">
@@ -819,9 +898,15 @@
         <v>1.79</v>
       </c>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="n">
-        <v>2</v>
+      <c r="G19" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.37</v>
       </c>
     </row>
     <row r="20">
@@ -839,10 +924,16 @@
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="H20" t="n">
         <v>2.29</v>
       </c>
-      <c r="H20" t="n">
-        <v>3</v>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.33</v>
       </c>
     </row>
     <row r="21">
@@ -860,10 +951,16 @@
         <v>2.89</v>
       </c>
       <c r="G21" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="H21" t="n">
         <v>2.29</v>
       </c>
-      <c r="H21" t="n">
-        <v>3</v>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.33</v>
       </c>
     </row>
   </sheetData>
@@ -882,7 +979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,7 +1015,17 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Harris Teeter</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Whole Foods</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>control_price</t>
         </is>
       </c>
     </row>
@@ -945,6 +1052,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>9.99</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I2" t="n">
+        <v>10.49</v>
       </c>
     </row>
     <row r="3">
@@ -961,7 +1074,13 @@
       <c r="F3" t="n">
         <v>2.79</v>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>2.79</v>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -975,8 +1094,12 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>12.99</v>
+      </c>
+      <c r="I4" t="n">
+        <v>13.99</v>
       </c>
     </row>
     <row r="5">
@@ -993,8 +1116,12 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
         <v>13.49</v>
+      </c>
+      <c r="I5" t="n">
+        <v>11.99</v>
       </c>
     </row>
     <row r="6">
@@ -1014,7 +1141,13 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="H6" t="n">
         <v>19.49</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16.99</v>
       </c>
     </row>
     <row r="7">
@@ -1035,6 +1168,8 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1054,6 +1189,8 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -1068,6 +1205,8 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -1082,6 +1221,8 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -1096,6 +1237,8 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1115,6 +1258,8 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1136,6 +1281,10 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>2.75</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -1152,6 +1301,10 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>2.75</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
@@ -1166,6 +1319,8 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
@@ -1176,11 +1331,19 @@
       <c r="C16" t="n">
         <v>3.99</v>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>2.29</v>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H16" t="n">
         <v>1.49</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.23</v>
       </c>
     </row>
     <row r="17">
@@ -1192,11 +1355,19 @@
       <c r="C17" t="n">
         <v>2.99</v>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>2.29</v>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H17" t="n">
         <v>1.49</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.79</v>
       </c>
     </row>
     <row r="18">
@@ -1214,6 +1385,10 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>1.37</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -1229,7 +1404,13 @@
         <v>1.5</v>
       </c>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>1.37</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
@@ -1246,7 +1427,13 @@
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="H20" t="n">
         <v>1.78</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.33</v>
       </c>
     </row>
     <row r="21">
@@ -1264,7 +1451,13 @@
         <v>2.89</v>
       </c>
       <c r="G21" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="H21" t="n">
         <v>1.78</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.33</v>
       </c>
     </row>
   </sheetData>
@@ -1437,7 +1630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:V83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1511,6 +1704,46 @@
           <t>found</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>storefront_price</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>amazon_total_wine_price</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>control_price</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>control_source</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>control_note</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>has_control</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>regular_premium_pct</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>paid_premium_pct</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1565,6 +1798,16 @@
       <c r="N2" t="b">
         <v>1</v>
       </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1619,6 +1862,32 @@
       <c r="N3" t="b">
         <v>1</v>
       </c>
+      <c r="O3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T3" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>28.32618025751072</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-14.16309012875536</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1671,6 +1940,16 @@
       <c r="N4" t="b">
         <v>1</v>
       </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1723,6 +2002,16 @@
       <c r="N5" t="b">
         <v>1</v>
       </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1775,6 +2064,16 @@
       <c r="N6" t="b">
         <v>1</v>
       </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1827,6 +2126,16 @@
       <c r="N7" t="b">
         <v>1</v>
       </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1879,6 +2188,16 @@
       <c r="N8" t="b">
         <v>1</v>
       </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1931,6 +2250,16 @@
       <c r="N9" t="b">
         <v>1</v>
       </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1985,6 +2314,32 @@
       <c r="N10" t="b">
         <v>1</v>
       </c>
+      <c r="O10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T10" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>28.32618025751072</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-14.16309012875536</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2037,6 +2392,28 @@
       <c r="N11" t="b">
         <v>1</v>
       </c>
+      <c r="O11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="b">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2089,6 +2466,28 @@
       <c r="N12" t="b">
         <v>1</v>
       </c>
+      <c r="O12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="b">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2141,6 +2540,32 @@
       <c r="N13" t="b">
         <v>1</v>
       </c>
+      <c r="O13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T13" t="b">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>45.25547445255474</v>
+      </c>
+      <c r="V13" t="n">
+        <v>45.25547445255474</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2193,6 +2618,32 @@
       <c r="N14" t="b">
         <v>1</v>
       </c>
+      <c r="O14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T14" t="b">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>45.25547445255474</v>
+      </c>
+      <c r="V14" t="n">
+        <v>45.25547445255474</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2245,6 +2696,32 @@
       <c r="N15" t="b">
         <v>1</v>
       </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2297,6 +2774,32 @@
       <c r="N16" t="b">
         <v>1</v>
       </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T16" t="b">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>8.340283569641361</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8.340283569641361</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2349,6 +2852,32 @@
       <c r="N17" t="b">
         <v>1</v>
       </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T17" t="b">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>35.31489111241908</v>
+      </c>
+      <c r="V17" t="n">
+        <v>35.31489111241908</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2401,21 +2930,47 @@
       <c r="N18" t="b">
         <v>1</v>
       </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T18" t="b">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>42.8979980934223</v>
+      </c>
+      <c r="V18" t="n">
+        <v>42.8979980934223</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RXBAR | Bluberry</t>
+          <t>Kind | Dark chocolate mocha almond, 12 oz bar</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RXBAR</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bluberry</t>
+          <t>Dark chocolate mocha almond, 12 oz bar</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2425,49 +2980,71 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gazelle</t>
+          <t>Durham Co-op</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>small store</t>
+          <t>co-op</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2.89</v>
+        <v>2.29</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Diff flavor</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>2.89</v>
+        <v>2.29</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>14.77 for 12, amazon official storefront</t>
+        </is>
+      </c>
+      <c r="T19" t="b">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>86.17886178861789</v>
+      </c>
+      <c r="V19" t="n">
+        <v>86.17886178861789</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RXBAR | Peanut butter</t>
+          <t>Kind | Peanut butter dark chocolate, 12 oz bar</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RXBAR</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Peanut butter</t>
+          <t>Peanut butter dark chocolate, 12 oz bar</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2477,16 +3054,16 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gazelle</t>
+          <t>Durham Co-op</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>small store</t>
+          <t>co-op</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2.89</v>
+        <v>2.29</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -2496,26 +3073,52 @@
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>2.89</v>
+        <v>2.29</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>13.33 for 12, amazon official storefront</t>
+        </is>
+      </c>
+      <c r="T20" t="b">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>189.873417721519</v>
+      </c>
+      <c r="V20" t="n">
+        <v>189.873417721519</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Big Spoon | Cherry chocolate</t>
+          <t>RXBAR | Bluberry</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Big Spoon</t>
+          <t>RXBAR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cherry chocolate</t>
+          <t>Bluberry</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2533,33 +3136,63 @@
           <t>small store</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>2.89</v>
+      </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Diff flavor</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>2.89</v>
+      </c>
       <c r="N21" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T21" t="b">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Big Spoon | Apricot pepita</t>
+          <t>RXBAR | Peanut butter</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Big Spoon</t>
+          <t>RXBAR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Apricot pepita</t>
+          <t>Peanut butter</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2577,7 +3210,9 @@
           <t>small store</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>2.89</v>
+      </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -2585,25 +3220,53 @@
         <v>0</v>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>2.89</v>
+      </c>
       <c r="N22" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T22" t="b">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>24.03433476394849</v>
+      </c>
+      <c r="V22" t="n">
+        <v>24.03433476394849</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Luna | Bluberry, 1.69 oz</t>
+          <t>Big Spoon | Cherry chocolate</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Luna</t>
+          <t>Big Spoon</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bluberry, 1.69 oz</t>
+          <t>Cherry chocolate</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2633,21 +3296,39 @@
       <c r="N23" t="b">
         <v>0</v>
       </c>
+      <c r="O23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="b">
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Luna | Lemon zest, 1.69</t>
+          <t>Big Spoon | Apricot pepita</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Luna</t>
+          <t>Big Spoon</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lemon zest, 1.69</t>
+          <t>Apricot pepita</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2677,26 +3358,44 @@
       <c r="N24" t="b">
         <v>0</v>
       </c>
+      <c r="O24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="b">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pisgah | 6 pack pale ale</t>
+          <t>Luna | Bluberry, 1.69 oz</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pisgah</t>
+          <t>Luna</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6 pack pale ale</t>
+          <t>Bluberry, 1.69 oz</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>beer</t>
+          <t>snack bar</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2721,26 +3420,48 @@
       <c r="N25" t="b">
         <v>0</v>
       </c>
+      <c r="O25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T25" t="b">
+        <v>1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ponysaurus | Biere de garde, 6 pk</t>
+          <t>Luna | Lemon zest, 1.69</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ponysaurus</t>
+          <t>Luna</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Biere de garde, 6 pk</t>
+          <t>Lemon zest, 1.69</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>beer</t>
+          <t>snack bar</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2765,21 +3486,43 @@
       <c r="N26" t="b">
         <v>0</v>
       </c>
+      <c r="O26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T26" t="b">
+        <v>1</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sierra Nevada | Pale ale 12 pk</t>
+          <t>Pisgah | 6 pack pale ale</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sierra Nevada</t>
+          <t>Pisgah</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pale ale 12 pk</t>
+          <t>6 pack pale ale</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2797,41 +3540,55 @@
           <t>small store</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>14.99</v>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>IPA; 6 pack</t>
-        </is>
-      </c>
-      <c r="M27" t="n">
-        <v>14.99</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T27" t="b">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Blue Ribbon | Narragansett, 12 pk lager cans</t>
+          <t>Ponysaurus | Biere de garde, 6 pk</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Blue Ribbon</t>
+          <t>Ponysaurus</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Narragansett, 12 pk lager cans</t>
+          <t>Biere de garde, 6 pk</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2861,21 +3618,43 @@
       <c r="N28" t="b">
         <v>0</v>
       </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T28" t="b">
+        <v>1</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Budweiser | 25 oz bud light</t>
+          <t>Sierra Nevada | Pale ale 12 pk</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Budweiser</t>
+          <t>Sierra Nevada</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>25 oz bud light</t>
+          <t>Pale ale 12 pk</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2894,46 +3673,72 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2.79</v>
+        <v>14.99</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>IPA; 6 pack</t>
+        </is>
+      </c>
       <c r="M29" t="n">
-        <v>2.79</v>
+        <v>14.99</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
       </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RXBAR | Bluberry</t>
+          <t>Blue Ribbon | Narragansett, 12 pk lager cans</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RXBAR</t>
+          <t>Blue Ribbon</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bluberry</t>
+          <t>Narragansett, 12 pk lager cans</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>snack bar</t>
+          <t>beer</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bulldega</t>
+          <t>Gazelle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2953,31 +3758,53 @@
       <c r="N30" t="b">
         <v>0</v>
       </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RXBAR | Peanut butter</t>
+          <t>Budweiser | 25 oz bud light</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RXBAR</t>
+          <t>Budweiser</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Peanut butter</t>
+          <t>25 oz bud light</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>snack bar</t>
+          <t>beer</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bulldega</t>
+          <t>Gazelle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2985,7 +3812,9 @@
           <t>small store</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>2.79</v>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
@@ -2993,25 +3822,53 @@
         <v>0</v>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>2.79</v>
+      </c>
       <c r="N31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T31" t="b">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Big Spoon | Cherry chocolate</t>
+          <t>RXBAR | Bluberry</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Big Spoon</t>
+          <t>RXBAR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cherry chocolate</t>
+          <t>Bluberry</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3029,9 +3886,7 @@
           <t>small store</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>3.19</v>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -3039,27 +3894,47 @@
         <v>0</v>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="n">
-        <v>3.19</v>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T32" t="b">
+        <v>1</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Big Spoon | Apricot pepita</t>
+          <t>RXBAR | Peanut butter</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Big Spoon</t>
+          <t>RXBAR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Apricot pepita</t>
+          <t>Peanut butter</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3077,9 +3952,7 @@
           <t>small store</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>3.19</v>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
@@ -3087,27 +3960,47 @@
         <v>0</v>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="n">
-        <v>3.19</v>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T33" t="b">
+        <v>1</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Luna | Bluberry, 1.69 oz</t>
+          <t>Big Spoon | Cherry chocolate</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Luna</t>
+          <t>Big Spoon</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bluberry, 1.69 oz</t>
+          <t>Cherry chocolate</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3126,7 +4019,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -3136,26 +4029,48 @@
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="b">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>15.99999999999999</v>
+      </c>
+      <c r="V34" t="n">
+        <v>15.99999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Luna | Lemon zest, 1.69</t>
+          <t>Big Spoon | Apricot pepita</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Luna</t>
+          <t>Big Spoon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lemon zest, 1.69</t>
+          <t>Apricot pepita</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3173,7 +4088,9 @@
           <t>small store</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>3.19</v>
+      </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
@@ -3181,30 +4098,54 @@
         <v>0</v>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>3.19</v>
+      </c>
       <c r="N35" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="b">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>15.99999999999999</v>
+      </c>
+      <c r="V35" t="n">
+        <v>15.99999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pisgah | 6 pack pale ale</t>
+          <t>Luna | Bluberry, 1.69 oz</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pisgah</t>
+          <t>Luna</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>6 pack pale ale</t>
+          <t>Bluberry, 1.69 oz</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>beer</t>
+          <t>snack bar</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3217,7 +4158,9 @@
           <t>small store</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>2.99</v>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
@@ -3225,30 +4168,58 @@
         <v>0</v>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>2.99</v>
+      </c>
       <c r="N36" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T36" t="b">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>118.2481751824818</v>
+      </c>
+      <c r="V36" t="n">
+        <v>118.2481751824818</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ponysaurus | Biere de garde, 6 pk</t>
+          <t>Luna | Lemon zest, 1.69</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ponysaurus</t>
+          <t>Luna</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Biere de garde, 6 pk</t>
+          <t>Lemon zest, 1.69</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>beer</t>
+          <t>snack bar</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3261,9 +4232,7 @@
           <t>small store</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>17.59</v>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -3271,27 +4240,47 @@
         <v>0</v>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="n">
-        <v>17.59</v>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T37" t="b">
+        <v>1</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sierra Nevada | Pale ale 12 pk</t>
+          <t>Pisgah | 6 pack pale ale</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sierra Nevada</t>
+          <t>Pisgah</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pale ale 12 pk</t>
+          <t>6 pack pale ale</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3309,9 +4298,7 @@
           <t>small store</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>31.99</v>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -3319,27 +4306,47 @@
         <v>0</v>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="n">
-        <v>31.99</v>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T38" t="b">
+        <v>1</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Blue Ribbon | Narragansett, 12 pk lager cans</t>
+          <t>Ponysaurus | Biere de garde, 6 pk</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Blue Ribbon</t>
+          <t>Ponysaurus</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Narragansett, 12 pk lager cans</t>
+          <t>Biere de garde, 6 pk</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3373,21 +4380,47 @@
       <c r="N39" t="b">
         <v>1</v>
       </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T39" t="b">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>46.70558798999165</v>
+      </c>
+      <c r="V39" t="n">
+        <v>46.70558798999165</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Budweiser | 25 oz bud light</t>
+          <t>Sierra Nevada | Pale ale 12 pk</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Budweiser</t>
+          <t>Sierra Nevada</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>25 oz bud light</t>
+          <t>Pale ale 12 pk</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3405,7 +4438,9 @@
           <t>small store</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>31.99</v>
+      </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
@@ -3413,30 +4448,58 @@
         <v>0</v>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="n">
+        <v>31.99</v>
+      </c>
       <c r="N40" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T40" t="b">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>88.28722778104768</v>
+      </c>
+      <c r="V40" t="n">
+        <v>88.28722778104768</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kind | Dark chocolate mocha almond, 12 oz bar</t>
+          <t>Blue Ribbon | Narragansett, 12 pk lager cans</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Blue Ribbon</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dark chocolate mocha almond, 12 oz bar</t>
+          <t>Narragansett, 12 pk lager cans</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>snack bar</t>
+          <t>beer</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3450,7 +4513,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>3.99</v>
+        <v>17.59</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -3460,31 +4523,57 @@
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
-        <v>3.99</v>
+        <v>17.59</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T41" t="b">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>67.68350810295519</v>
+      </c>
+      <c r="V41" t="n">
+        <v>67.68350810295519</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kind | Peanut butter dark chocolate, 12 oz bar</t>
+          <t>Budweiser | 25 oz bud light</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Budweiser</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Peanut butter dark chocolate, 12 oz bar</t>
+          <t>25 oz bud light</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>snack bar</t>
+          <t>beer</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3497,9 +4586,7 @@
           <t>small store</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>2.99</v>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
@@ -3507,27 +4594,47 @@
         <v>0</v>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="n">
-        <v>2.99</v>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T42" t="b">
+        <v>1</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RXBAR | Bluberry</t>
+          <t>Kind | Dark chocolate mocha almond, 12 oz bar</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RXBAR</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bluberry</t>
+          <t>Dark chocolate mocha almond, 12 oz bar</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3537,49 +4644,71 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Whole Foods</t>
+          <t>Bulldega</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>chain</t>
+          <t>small store</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1.6</v>
-      </c>
+        <v>3.99</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="b">
         <v>0</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
-        <v>1.78</v>
+        <v>3.99</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>14.77 for 12, amazon official storefront</t>
+        </is>
+      </c>
+      <c r="T43" t="b">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>224.390243902439</v>
+      </c>
+      <c r="V43" t="n">
+        <v>224.390243902439</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RXBAR | Peanut butter</t>
+          <t>Kind | Peanut butter dark chocolate, 12 oz bar</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RXBAR</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Peanut butter</t>
+          <t>Peanut butter dark chocolate, 12 oz bar</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3589,49 +4718,71 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Whole Foods</t>
+          <t>Bulldega</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>chain</t>
+          <t>small store</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1.6</v>
-      </c>
+        <v>2.99</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="b">
         <v>0</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
-        <v>1.78</v>
+        <v>2.99</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>13.33 for 12, amazon official storefront</t>
+        </is>
+      </c>
+      <c r="T44" t="b">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>278.4810126582279</v>
+      </c>
+      <c r="V44" t="n">
+        <v>278.4810126582279</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Big Spoon | Cherry chocolate</t>
+          <t>RXBAR | Bluberry</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Big Spoon</t>
+          <t>RXBAR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cherry chocolate</t>
+          <t>Bluberry</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3649,33 +4800,67 @@
           <t>chain</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.6</v>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="b">
         <v>0</v>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="n">
+        <v>1.78</v>
+      </c>
       <c r="N45" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T45" t="b">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>-1.716738197424894</v>
+      </c>
+      <c r="V45" t="n">
+        <v>-23.60515021459227</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Big Spoon | Apricot pepita</t>
+          <t>RXBAR | Peanut butter</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Big Spoon</t>
+          <t>RXBAR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Apricot pepita</t>
+          <t>Peanut butter</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3693,33 +4878,67 @@
           <t>chain</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="G46" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.6</v>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="b">
         <v>0</v>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="n">
+        <v>1.78</v>
+      </c>
       <c r="N46" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T46" t="b">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>-1.716738197424894</v>
+      </c>
+      <c r="V46" t="n">
+        <v>-23.60515021459227</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Luna | Bluberry, 1.69 oz</t>
+          <t>Big Spoon | Cherry chocolate</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Luna</t>
+          <t>Big Spoon</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bluberry, 1.69 oz</t>
+          <t>Cherry chocolate</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3749,21 +4968,39 @@
       <c r="N47" t="b">
         <v>0</v>
       </c>
+      <c r="O47" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="b">
+        <v>1</v>
+      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Luna | Lemon zest, 1.69</t>
+          <t>Big Spoon | Apricot pepita</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Luna</t>
+          <t>Big Spoon</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lemon zest, 1.69</t>
+          <t>Apricot pepita</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3793,26 +5030,44 @@
       <c r="N48" t="b">
         <v>0</v>
       </c>
+      <c r="O48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="b">
+        <v>1</v>
+      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pisgah | 6 pack pale ale</t>
+          <t>Luna | Bluberry, 1.69 oz</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pisgah</t>
+          <t>Luna</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>6 pack pale ale</t>
+          <t>Bluberry, 1.69 oz</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>beer</t>
+          <t>snack bar</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3825,9 +5080,7 @@
           <t>chain</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>12.99</v>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
@@ -3835,32 +5088,52 @@
         <v>0</v>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="n">
-        <v>12.99</v>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T49" t="b">
+        <v>1</v>
+      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ponysaurus | Biere de garde, 6 pk</t>
+          <t>Luna | Lemon zest, 1.69</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ponysaurus</t>
+          <t>Luna</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Biere de garde, 6 pk</t>
+          <t>Lemon zest, 1.69</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>beer</t>
+          <t>snack bar</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3873,9 +5146,7 @@
           <t>chain</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>13.49</v>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
@@ -3883,27 +5154,47 @@
         <v>0</v>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="n">
-        <v>13.49</v>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T50" t="b">
+        <v>1</v>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sierra Nevada | Pale ale 12 pk</t>
+          <t>Pisgah | 6 pack pale ale</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sierra Nevada</t>
+          <t>Pisgah</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pale ale 12 pk</t>
+          <t>6 pack pale ale</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3922,7 +5213,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>19.49</v>
+        <v>12.99</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -3932,26 +5223,52 @@
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
-        <v>19.49</v>
+        <v>12.99</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T51" t="b">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>-7.147962830593279</v>
+      </c>
+      <c r="V51" t="n">
+        <v>-7.147962830593279</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Blue Ribbon | Narragansett, 12 pk lager cans</t>
+          <t>Ponysaurus | Biere de garde, 6 pk</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Blue Ribbon</t>
+          <t>Ponysaurus</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Narragansett, 12 pk lager cans</t>
+          <t>Biere de garde, 6 pk</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3970,40 +5287,62 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>9.99</v>
+        <v>13.49</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>bottom</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="b">
         <v>0</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
-        <v>9.99</v>
+        <v>13.49</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T52" t="b">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>12.51042535446205</v>
+      </c>
+      <c r="V52" t="n">
+        <v>12.51042535446205</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Budweiser | 25 oz bud light</t>
+          <t>Sierra Nevada | Pale ale 12 pk</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Budweiser</t>
+          <t>Sierra Nevada</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>25 oz bud light</t>
+          <t>Pale ale 12 pk</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4021,42 +5360,68 @@
           <t>chain</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="n">
+        <v>19.49</v>
+      </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="b">
-        <v>1</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>price note: 4.58 (11 cents / oz pack of 6 for $7.99)</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="n">
+        <v>19.49</v>
+      </c>
       <c r="N53" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T53" t="b">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>14.71453796350795</v>
+      </c>
+      <c r="V53" t="n">
+        <v>14.71453796350795</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kind | Dark chocolate mocha almond, 12 oz bar</t>
+          <t>Blue Ribbon | Narragansett, 12 pk lager cans</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Blue Ribbon</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dark chocolate mocha almond, 12 oz bar</t>
+          <t>Narragansett, 12 pk lager cans</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>snack bar</t>
+          <t>beer</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4070,11 +5435,9 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="H54" t="n">
-        <v>1.49</v>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
@@ -4086,31 +5449,57 @@
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
-        <v>1.49</v>
+        <v>9.99</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T54" t="b">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>-4.766444232602474</v>
+      </c>
+      <c r="V54" t="n">
+        <v>-4.766444232602474</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kind | Peanut butter dark chocolate, 12 oz bar</t>
+          <t>Budweiser | 25 oz bud light</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Budweiser</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Peanut butter dark chocolate, 12 oz bar</t>
+          <t>25 oz bud light</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>snack bar</t>
+          <t>beer</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4123,43 +5512,59 @@
           <t>chain</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="H55" t="n">
-        <v>1.49</v>
-      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bottom</t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="b">
-        <v>0</v>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="n">
-        <v>1.49</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>price note: 4.58 (11 cents / oz pack of 6 for $7.99)</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T55" t="b">
+        <v>1</v>
+      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RXBAR | Bluberry</t>
+          <t>Kind | Dark chocolate mocha almond, 12 oz bar</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RXBAR</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bluberry</t>
+          <t>Dark chocolate mocha almond, 12 oz bar</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4169,7 +5574,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Food Lion</t>
+          <t>Whole Foods</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4178,38 +5583,68 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>2.49</v>
+        <v>1.66</v>
       </c>
       <c r="H56" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bottom</t>
+        </is>
+      </c>
       <c r="K56" t="b">
         <v>0</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>14.77 for 12, amazon official storefront</t>
+        </is>
+      </c>
+      <c r="T56" t="b">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>34.95934959349594</v>
+      </c>
+      <c r="V56" t="n">
+        <v>21.13821138211382</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RXBAR | Peanut butter</t>
+          <t>Kind | Peanut butter dark chocolate, 12 oz bar</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RXBAR</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Peanut butter</t>
+          <t>Peanut butter dark chocolate, 12 oz bar</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4219,7 +5654,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Food Lion</t>
+          <t>Whole Foods</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4228,42 +5663,68 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2.19</v>
+        <v>1.66</v>
       </c>
       <c r="H57" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bottom</t>
+        </is>
+      </c>
       <c r="K57" t="b">
-        <v>1</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>PB Chocolate</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>13.33 for 12, amazon official storefront</t>
+        </is>
+      </c>
+      <c r="T57" t="b">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>110.126582278481</v>
+      </c>
+      <c r="V57" t="n">
+        <v>88.60759493670885</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Big Spoon | Cherry chocolate</t>
+          <t>RXBAR | Bluberry</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Big Spoon</t>
+          <t>RXBAR</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cherry chocolate</t>
+          <t>Bluberry</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4281,33 +5742,65 @@
           <t>chain</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.69</v>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="b">
         <v>0</v>
       </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+      <c r="M58" t="n">
+        <v>1.69</v>
+      </c>
       <c r="N58" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T58" t="b">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>6.866952789699576</v>
+      </c>
+      <c r="V58" t="n">
+        <v>-27.46781115879828</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Big Spoon | Apricot pepita</t>
+          <t>RXBAR | Peanut butter</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Big Spoon</t>
+          <t>RXBAR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Apricot pepita</t>
+          <t>Peanut butter</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4325,33 +5818,65 @@
           <t>chain</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.69</v>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="b">
-        <v>0</v>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>PB Chocolate</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>1.69</v>
+      </c>
       <c r="N59" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O59" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T59" t="b">
+        <v>1</v>
+      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Luna | Bluberry, 1.69 oz</t>
+          <t>Big Spoon | Cherry chocolate</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Luna</t>
+          <t>Big Spoon</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bluberry, 1.69 oz</t>
+          <t>Cherry chocolate</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4381,21 +5906,39 @@
       <c r="N60" t="b">
         <v>0</v>
       </c>
+      <c r="O60" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="b">
+        <v>1</v>
+      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Luna | Lemon zest, 1.69</t>
+          <t>Big Spoon | Apricot pepita</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Luna</t>
+          <t>Big Spoon</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lemon zest, 1.69</t>
+          <t>Apricot pepita</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4413,44 +5956,56 @@
           <t>chain</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="H61" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="b">
         <v>0</v>
       </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="b">
+        <v>1</v>
+      </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Pisgah | 6 pack pale ale</t>
+          <t>Luna | Bluberry, 1.69 oz</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pisgah</t>
+          <t>Luna</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>6 pack pale ale</t>
+          <t>Bluberry, 1.69 oz</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>beer</t>
+          <t>snack bar</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4475,26 +6030,48 @@
       <c r="N62" t="b">
         <v>0</v>
       </c>
+      <c r="O62" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T62" t="b">
+        <v>1</v>
+      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ponysaurus | Biere de garde, 6 pk</t>
+          <t>Luna | Lemon zest, 1.69</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ponysaurus</t>
+          <t>Luna</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Biere de garde, 6 pk</t>
+          <t>Lemon zest, 1.69</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>beer</t>
+          <t>snack bar</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4507,33 +6084,65 @@
           <t>chain</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.5</v>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="b">
         <v>0</v>
       </c>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+      <c r="M63" t="n">
+        <v>1.5</v>
+      </c>
       <c r="N63" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T63" t="b">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>30.65693430656933</v>
+      </c>
+      <c r="V63" t="n">
+        <v>9.48905109489051</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sierra Nevada | Pale ale 12 pk</t>
+          <t>Pisgah | 6 pack pale ale</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sierra Nevada</t>
+          <t>Pisgah</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pale ale 12 pk</t>
+          <t>6 pack pale ale</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4551,41 +6160,55 @@
           <t>chain</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>20.99</v>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="b">
         <v>0</v>
       </c>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="n">
-        <v>20.99</v>
-      </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T64" t="b">
+        <v>1</v>
+      </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Blue Ribbon | Narragansett, 12 pk lager cans</t>
+          <t>Ponysaurus | Biere de garde, 6 pk</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Blue Ribbon</t>
+          <t>Ponysaurus</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Narragansett, 12 pk lager cans</t>
+          <t>Biere de garde, 6 pk</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4603,41 +6226,55 @@
           <t>chain</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>10.49</v>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>middle to bottom</t>
-        </is>
-      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="b">
         <v>0</v>
       </c>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="n">
-        <v>10.49</v>
-      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T65" t="b">
+        <v>1</v>
+      </c>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Budweiser | 25 oz bud light</t>
+          <t>Sierra Nevada | Pale ale 12 pk</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Budweiser</t>
+          <t>Sierra Nevada</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>25 oz bud light</t>
+          <t>Pale ale 12 pk</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4656,13 +6293,13 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>2.59</v>
+        <v>20.99</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>middle to too</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="K66" t="b">
@@ -4670,31 +6307,57 @@
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
-        <v>2.59</v>
+        <v>20.99</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T66" t="b">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>23.54326074161273</v>
+      </c>
+      <c r="V66" t="n">
+        <v>23.54326074161273</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kind | Dark chocolate mocha almond, 12 oz bar</t>
+          <t>Blue Ribbon | Narragansett, 12 pk lager cans</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Blue Ribbon</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dark chocolate mocha almond, 12 oz bar</t>
+          <t>Narragansett, 12 pk lager cans</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>snack bar</t>
+          <t>beer</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4708,45 +6371,71 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1.79</v>
+        <v>10.49</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>middle to bottom</t>
+        </is>
+      </c>
       <c r="K67" t="b">
-        <v>1</v>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Caramel almond</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
-        <v>1.79</v>
+        <v>10.49</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T67" t="b">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kind | Peanut butter dark chocolate, 12 oz bar</t>
+          <t>Budweiser | 25 oz bud light</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Budweiser</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Peanut butter dark chocolate, 12 oz bar</t>
+          <t>25 oz bud light</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>snack bar</t>
+          <t>beer</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4760,24 +6449,1602 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1.79</v>
+        <v>2.59</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>middle to too</t>
+        </is>
+      </c>
       <c r="K68" t="b">
-        <v>1</v>
-      </c>
-      <c r="L68" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="N68" t="b">
+        <v>1</v>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T68" t="b">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>-7.168458781362008</v>
+      </c>
+      <c r="V68" t="n">
+        <v>-7.168458781362008</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Kind | Dark chocolate mocha almond, 12 oz bar</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Dark chocolate mocha almond, 12 oz bar</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>snack bar</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Food Lion</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="b">
+        <v>1</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Caramel almond</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="N69" t="b">
+        <v>1</v>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>14.77 for 12, amazon official storefront</t>
+        </is>
+      </c>
+      <c r="T69" t="b">
+        <v>1</v>
+      </c>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Kind | Peanut butter dark chocolate, 12 oz bar</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Peanut butter dark chocolate, 12 oz bar</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>snack bar</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Food Lion</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="b">
+        <v>1</v>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t>Almond and sea salt</t>
         </is>
       </c>
-      <c r="M68" t="n">
+      <c r="M70" t="n">
         <v>1.79</v>
       </c>
-      <c r="N68" t="b">
-        <v>1</v>
+      <c r="N70" t="b">
+        <v>1</v>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>13.33 for 12, amazon official storefront</t>
+        </is>
+      </c>
+      <c r="T70" t="b">
+        <v>1</v>
+      </c>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>RXBAR | Bluberry</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>RXBAR</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Bluberry</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>snack bar</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Harris Teeter</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="N71" t="b">
+        <v>1</v>
+      </c>
+      <c r="O71" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T71" t="b">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>15.45064377682404</v>
+      </c>
+      <c r="V71" t="n">
+        <v>15.45064377682404</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>RXBAR | Peanut butter</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>RXBAR</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Peanut butter</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>snack bar</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Harris Teeter</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="N72" t="b">
+        <v>1</v>
+      </c>
+      <c r="O72" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T72" t="b">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>15.45064377682404</v>
+      </c>
+      <c r="V72" t="n">
+        <v>15.45064377682404</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Big Spoon | Cherry chocolate</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Big Spoon</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Cherry chocolate</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>snack bar</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Harris Teeter</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="b">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="b">
+        <v>1</v>
+      </c>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Big Spoon | Apricot pepita</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Big Spoon</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Apricot pepita</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>snack bar</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Harris Teeter</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="b">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="b">
+        <v>1</v>
+      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Luna | Bluberry, 1.69 oz</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Luna</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Bluberry, 1.69 oz</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>snack bar</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Harris Teeter</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="b">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T75" t="b">
+        <v>1</v>
+      </c>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Luna | Lemon zest, 1.69</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Luna</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Lemon zest, 1.69</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>snack bar</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Harris Teeter</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="N76" t="b">
+        <v>1</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T76" t="b">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>52.55474452554743</v>
+      </c>
+      <c r="V76" t="n">
+        <v>52.55474452554743</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Pisgah | 6 pack pale ale</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Pisgah</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>6 pack pale ale</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>beer</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Harris Teeter</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="b">
+        <v>0</v>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T77" t="b">
+        <v>1</v>
+      </c>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ponysaurus | Biere de garde, 6 pk</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Ponysaurus</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Biere de garde, 6 pk</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>beer</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Harris Teeter</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="b">
+        <v>0</v>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T78" t="b">
+        <v>1</v>
+      </c>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Sierra Nevada | Pale ale 12 pk</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Sierra Nevada</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Pale ale 12 pk</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>beer</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Harris Teeter</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="N79" t="b">
+        <v>1</v>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T79" t="b">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>-5.885815185403165</v>
+      </c>
+      <c r="V79" t="n">
+        <v>-5.885815185403165</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Blue Ribbon | Narragansett, 12 pk lager cans</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Blue Ribbon</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Narragansett, 12 pk lager cans</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>beer</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Harris Teeter</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="N80" t="b">
+        <v>1</v>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T80" t="b">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>-4.766444232602474</v>
+      </c>
+      <c r="V80" t="n">
+        <v>-4.766444232602474</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Budweiser | 25 oz bud light</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Budweiser</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>25 oz bud light</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>beer</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Harris Teeter</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="b">
+        <v>0</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N81" t="b">
+        <v>1</v>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T81" t="b">
+        <v>1</v>
+      </c>
+      <c r="U81" t="n">
+        <v>7.168458781362008</v>
+      </c>
+      <c r="V81" t="n">
+        <v>7.168458781362008</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Kind | Dark chocolate mocha almond, 12 oz bar</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Dark chocolate mocha almond, 12 oz bar</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>snack bar</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Harris Teeter</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="b">
+        <v>0</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="N82" t="b">
+        <v>1</v>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>14.77 for 12, amazon official storefront</t>
+        </is>
+      </c>
+      <c r="T82" t="b">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>61.78861788617886</v>
+      </c>
+      <c r="V82" t="n">
+        <v>61.78861788617886</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Kind | Peanut butter dark chocolate, 12 oz bar</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Peanut butter dark chocolate, 12 oz bar</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>snack bar</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Harris Teeter</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="b">
+        <v>0</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="N83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>13.33 for 12, amazon official storefront</t>
+        </is>
+      </c>
+      <c r="T83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U83" t="n">
+        <v>151.8987341772151</v>
+      </c>
+      <c r="V83" t="n">
+        <v>151.8987341772151</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storefront_price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>amazon_total_wine_price</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>control_price</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>control_source</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>control_note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RXBAR | Bluberry</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RXBAR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bluberry</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RXBAR | Peanut Butter</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RXBAR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Peanut Butter</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Big Spoon | Cherry chocolate</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Big Spoon</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cherry chocolate</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Big Spoon | Apricot pepita</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Big Spoon</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apricot pepita</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Luna | Bluberry, 1.69 oz</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Luna</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bluberry, 1.69 oz</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Luna | Lemon zest, 1.69</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Luna</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lemon zest, 1.69</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kind | Dark chocolate mocha almond, 12 oz bar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Dark chocolate mocha almond, 12 oz bar</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>14.77 for 12, amazon official storefront</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kind | Peanut butter dark chocolate, 12 oz bar</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Peanut butter dark chocolate, 12 oz bar</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>13.33 for 12, amazon official storefront</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Pisgah | 6 pack pale ale</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pisgah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6 pack pale ale</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="F10" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ponysaurus | Biere de garde, 6 pk</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ponysaurus</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Biere de garde, 6 pk</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sierra Nevada | Pale ale 12 pk</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sierra Nevada</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pale ale 12 pk</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F12" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Blue Ribbon | Narragansett, 12 pk lager cans</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Blue Ribbon</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Narragansett, 12 pk lager cans</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Budweiser | 25 oz bud light</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Budweiser</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>25 oz bud light</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/clean/price_table.xlsx
+++ b/data/clean/price_table.xlsx
@@ -11,6 +11,7 @@
     <sheet name="paid_price" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="substitutes_removed" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="long_data" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="control_data" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +21,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -45,12 +49,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,58 +450,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Bulldega</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Durham Co-op</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Food Lion</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Gazelle</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Whole Foods</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>n_stores</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>control_price</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>beer</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Blue Ribbon | Narragansett, 12 pk lager cans</t>
         </is>
@@ -488,9 +527,13 @@
       <c r="H2" t="n">
         <v>4</v>
       </c>
+      <c r="I2" t="n">
+        <v>10.49</v>
+      </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Budweiser | 25 oz bud light</t>
         </is>
@@ -507,9 +550,13 @@
       <c r="H3" t="n">
         <v>2</v>
       </c>
+      <c r="I3" t="n">
+        <v>2.79</v>
+      </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Pisgah | 6 pack pale ale</t>
         </is>
@@ -526,9 +573,13 @@
       <c r="H4" t="n">
         <v>2</v>
       </c>
+      <c r="I4" t="n">
+        <v>13.99</v>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Ponysaurus | Biere de garde, 6 pk</t>
         </is>
@@ -547,9 +598,13 @@
       <c r="H5" t="n">
         <v>3</v>
       </c>
+      <c r="I5" t="n">
+        <v>11.99</v>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>Sierra Nevada | Pale ale 12 pk</t>
         </is>
@@ -570,14 +625,17 @@
       <c r="H6" t="n">
         <v>4</v>
       </c>
+      <c r="I6" t="n">
+        <v>16.99</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>Organic Valley | Organic 2%, 64 fz</t>
         </is>
@@ -592,14 +650,15 @@
       <c r="H7" t="n">
         <v>1</v>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>pantry</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>Annie's | Classic cheddar pasta, 6 oz</t>
         </is>
@@ -614,9 +673,11 @@
       <c r="H8" t="n">
         <v>1</v>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>Annie's | Organic classic cheddar pasta, 6 oz</t>
         </is>
@@ -631,9 +692,11 @@
       <c r="H9" t="n">
         <v>1</v>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>Jovial | Gf elbows</t>
         </is>
@@ -648,9 +711,11 @@
       <c r="H10" t="n">
         <v>1</v>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>Jovial | Gf penne</t>
         </is>
@@ -665,14 +730,15 @@
       <c r="H11" t="n">
         <v>1</v>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>snack</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>Kettle brand | Sour cream and onion, 5 oz</t>
         </is>
@@ -687,14 +753,15 @@
       <c r="H12" t="n">
         <v>1</v>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>snack bar</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>Big Spoon | Apricot pepita</t>
         </is>
@@ -711,9 +778,13 @@
       <c r="H13" t="n">
         <v>2</v>
       </c>
+      <c r="I13" t="n">
+        <v>2.75</v>
+      </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>Big Spoon | Cherry chocolate</t>
         </is>
@@ -730,9 +801,13 @@
       <c r="H14" t="n">
         <v>2</v>
       </c>
+      <c r="I14" t="n">
+        <v>2.75</v>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>Hu chocolate | Almond butter + puffed quinoa dark chocolate</t>
         </is>
@@ -747,9 +822,11 @@
       <c r="H15" t="n">
         <v>1</v>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>Kind | Dark chocolate mocha almond, 12 oz bar</t>
         </is>
@@ -766,9 +843,13 @@
       <c r="H16" t="n">
         <v>2</v>
       </c>
+      <c r="I16" t="n">
+        <v>1.23</v>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>Kind | Peanut butter dark chocolate, 12 oz bar</t>
         </is>
@@ -785,9 +866,13 @@
       <c r="H17" t="n">
         <v>2</v>
       </c>
+      <c r="I17" t="n">
+        <v>0.79</v>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>Luna | Bluberry, 1.69 oz</t>
         </is>
@@ -804,9 +889,13 @@
       <c r="H18" t="n">
         <v>2</v>
       </c>
+      <c r="I18" t="n">
+        <v>1.37</v>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>Luna | Lemon zest, 1.69</t>
         </is>
@@ -823,9 +912,13 @@
       <c r="H19" t="n">
         <v>2</v>
       </c>
+      <c r="I19" t="n">
+        <v>1.37</v>
+      </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>RXBAR | Bluberry</t>
         </is>
@@ -844,9 +937,13 @@
       <c r="H20" t="n">
         <v>3</v>
       </c>
+      <c r="I20" t="n">
+        <v>2.33</v>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>RXBAR | Peanut butter</t>
         </is>
@@ -864,6 +961,9 @@
       </c>
       <c r="H21" t="n">
         <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.33</v>
       </c>
     </row>
   </sheetData>
@@ -882,53 +982,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Bulldega</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Durham Co-op</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Food Lion</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Gazelle</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Whole Foods</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>control_price</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>beer</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Blue Ribbon | Narragansett, 12 pk lager cans</t>
         </is>
@@ -946,9 +1051,13 @@
       <c r="G2" t="n">
         <v>9.99</v>
       </c>
+      <c r="H2" t="n">
+        <v>10.49</v>
+      </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Budweiser | 25 oz bud light</t>
         </is>
@@ -962,9 +1071,13 @@
         <v>2.79</v>
       </c>
       <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>2.79</v>
+      </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Pisgah | 6 pack pale ale</t>
         </is>
@@ -978,9 +1091,13 @@
       <c r="G4" t="n">
         <v>12.99</v>
       </c>
+      <c r="H4" t="n">
+        <v>13.99</v>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Ponysaurus | Biere de garde, 6 pk</t>
         </is>
@@ -996,9 +1113,13 @@
       <c r="G5" t="n">
         <v>13.49</v>
       </c>
+      <c r="H5" t="n">
+        <v>11.99</v>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>Sierra Nevada | Pale ale 12 pk</t>
         </is>
@@ -1016,14 +1137,17 @@
       <c r="G6" t="n">
         <v>19.49</v>
       </c>
+      <c r="H6" t="n">
+        <v>16.99</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>Organic Valley | Organic 2%, 64 fz</t>
         </is>
@@ -1035,14 +1159,15 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>pantry</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>Annie's | Classic cheddar pasta, 6 oz</t>
         </is>
@@ -1054,9 +1179,11 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>Annie's | Organic classic cheddar pasta, 6 oz</t>
         </is>
@@ -1068,9 +1195,11 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>Jovial | Gf elbows</t>
         </is>
@@ -1082,9 +1211,11 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>Jovial | Gf penne</t>
         </is>
@@ -1096,14 +1227,15 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>snack</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>Kettle brand | Sour cream and onion, 5 oz</t>
         </is>
@@ -1115,14 +1247,15 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>snack bar</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>Big Spoon | Apricot pepita</t>
         </is>
@@ -1136,9 +1269,13 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>2.75</v>
+      </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>Big Spoon | Cherry chocolate</t>
         </is>
@@ -1152,9 +1289,13 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>2.75</v>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>Hu chocolate | Almond butter + puffed quinoa dark chocolate</t>
         </is>
@@ -1166,9 +1307,11 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>Kind | Dark chocolate mocha almond, 12 oz bar</t>
         </is>
@@ -1182,9 +1325,13 @@
       <c r="G16" t="n">
         <v>1.49</v>
       </c>
+      <c r="H16" t="n">
+        <v>1.23</v>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>Kind | Peanut butter dark chocolate, 12 oz bar</t>
         </is>
@@ -1198,9 +1345,13 @@
       <c r="G17" t="n">
         <v>1.49</v>
       </c>
+      <c r="H17" t="n">
+        <v>0.79</v>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>Luna | Bluberry, 1.69 oz</t>
         </is>
@@ -1214,9 +1365,13 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>1.37</v>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>Luna | Lemon zest, 1.69</t>
         </is>
@@ -1230,9 +1385,13 @@
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>1.37</v>
+      </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>RXBAR | Bluberry</t>
         </is>
@@ -1248,9 +1407,13 @@
       <c r="G20" t="n">
         <v>1.78</v>
       </c>
+      <c r="H20" t="n">
+        <v>2.33</v>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>RXBAR | Peanut butter</t>
         </is>
@@ -1265,6 +1428,9 @@
       </c>
       <c r="G21" t="n">
         <v>1.78</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.33</v>
       </c>
     </row>
   </sheetData>
@@ -1287,22 +1453,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>store</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>regular_price</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1437,78 +1603,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:V68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>store</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>store_type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>regular_price</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sale_price</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>member_price</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>shelf</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>substitute</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>paid_price</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>found</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>storefront_price</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>amazon_total_wine_price</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>control_price</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>control_source</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>control_note</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>has_control</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>regular_premium_pct</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>paid_premium_pct</t>
         </is>
       </c>
     </row>
@@ -1565,6 +1771,16 @@
       <c r="N2" t="b">
         <v>1</v>
       </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1619,6 +1835,32 @@
       <c r="N3" t="b">
         <v>1</v>
       </c>
+      <c r="O3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T3" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>28.32618025751072</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-14.16309012875536</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1671,6 +1913,16 @@
       <c r="N4" t="b">
         <v>1</v>
       </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1723,6 +1975,16 @@
       <c r="N5" t="b">
         <v>1</v>
       </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1775,6 +2037,16 @@
       <c r="N6" t="b">
         <v>1</v>
       </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1827,6 +2099,16 @@
       <c r="N7" t="b">
         <v>1</v>
       </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1879,6 +2161,16 @@
       <c r="N8" t="b">
         <v>1</v>
       </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1931,6 +2223,16 @@
       <c r="N9" t="b">
         <v>1</v>
       </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1985,6 +2287,32 @@
       <c r="N10" t="b">
         <v>1</v>
       </c>
+      <c r="O10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T10" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>28.32618025751072</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-14.16309012875536</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2037,6 +2365,28 @@
       <c r="N11" t="b">
         <v>1</v>
       </c>
+      <c r="O11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="b">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2089,6 +2439,28 @@
       <c r="N12" t="b">
         <v>1</v>
       </c>
+      <c r="O12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="b">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2141,6 +2513,32 @@
       <c r="N13" t="b">
         <v>1</v>
       </c>
+      <c r="O13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T13" t="b">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>45.25547445255474</v>
+      </c>
+      <c r="V13" t="n">
+        <v>45.25547445255474</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2193,6 +2591,32 @@
       <c r="N14" t="b">
         <v>1</v>
       </c>
+      <c r="O14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T14" t="b">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>45.25547445255474</v>
+      </c>
+      <c r="V14" t="n">
+        <v>45.25547445255474</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2245,6 +2669,32 @@
       <c r="N15" t="b">
         <v>1</v>
       </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2297,6 +2747,32 @@
       <c r="N16" t="b">
         <v>1</v>
       </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T16" t="b">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>8.340283569641361</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8.340283569641361</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2349,6 +2825,32 @@
       <c r="N17" t="b">
         <v>1</v>
       </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T17" t="b">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>35.31489111241908</v>
+      </c>
+      <c r="V17" t="n">
+        <v>35.31489111241908</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2400,6 +2902,32 @@
       </c>
       <c r="N18" t="b">
         <v>1</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T18" t="b">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>42.8979980934223</v>
+      </c>
+      <c r="V18" t="n">
+        <v>42.8979980934223</v>
       </c>
     </row>
     <row r="19">
@@ -2453,6 +2981,28 @@
       <c r="N19" t="b">
         <v>1</v>
       </c>
+      <c r="O19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T19" t="b">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2500,6 +3050,32 @@
       </c>
       <c r="N20" t="b">
         <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T20" t="b">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>24.03433476394849</v>
+      </c>
+      <c r="V20" t="n">
+        <v>24.03433476394849</v>
       </c>
     </row>
     <row r="21">
@@ -2545,6 +3121,24 @@
       <c r="N21" t="b">
         <v>0</v>
       </c>
+      <c r="O21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="b">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2589,6 +3183,24 @@
       <c r="N22" t="b">
         <v>0</v>
       </c>
+      <c r="O22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="b">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2633,6 +3245,28 @@
       <c r="N23" t="b">
         <v>0</v>
       </c>
+      <c r="O23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T23" t="b">
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2677,6 +3311,28 @@
       <c r="N24" t="b">
         <v>0</v>
       </c>
+      <c r="O24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T24" t="b">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2721,6 +3377,28 @@
       <c r="N25" t="b">
         <v>0</v>
       </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T25" t="b">
+        <v>1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2765,6 +3443,28 @@
       <c r="N26" t="b">
         <v>0</v>
       </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T26" t="b">
+        <v>1</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2817,6 +3517,28 @@
       <c r="N27" t="b">
         <v>1</v>
       </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T27" t="b">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2861,6 +3583,28 @@
       <c r="N28" t="b">
         <v>0</v>
       </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T28" t="b">
+        <v>1</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2908,6 +3652,32 @@
       </c>
       <c r="N29" t="b">
         <v>1</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2953,6 +3723,28 @@
       <c r="N30" t="b">
         <v>0</v>
       </c>
+      <c r="O30" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2997,6 +3789,28 @@
       <c r="N31" t="b">
         <v>0</v>
       </c>
+      <c r="O31" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T31" t="b">
+        <v>1</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3045,6 +3859,28 @@
       <c r="N32" t="b">
         <v>1</v>
       </c>
+      <c r="O32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="b">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>15.99999999999999</v>
+      </c>
+      <c r="V32" t="n">
+        <v>15.99999999999999</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3093,6 +3929,28 @@
       <c r="N33" t="b">
         <v>1</v>
       </c>
+      <c r="O33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="b">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>15.99999999999999</v>
+      </c>
+      <c r="V33" t="n">
+        <v>15.99999999999999</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3140,6 +3998,32 @@
       </c>
       <c r="N34" t="b">
         <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T34" t="b">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>118.2481751824818</v>
+      </c>
+      <c r="V34" t="n">
+        <v>118.2481751824818</v>
       </c>
     </row>
     <row r="35">
@@ -3185,6 +4069,28 @@
       <c r="N35" t="b">
         <v>0</v>
       </c>
+      <c r="O35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T35" t="b">
+        <v>1</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3229,6 +4135,28 @@
       <c r="N36" t="b">
         <v>0</v>
       </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T36" t="b">
+        <v>1</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3277,6 +4205,32 @@
       <c r="N37" t="b">
         <v>1</v>
       </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T37" t="b">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>46.70558798999165</v>
+      </c>
+      <c r="V37" t="n">
+        <v>46.70558798999165</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3325,6 +4279,32 @@
       <c r="N38" t="b">
         <v>1</v>
       </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T38" t="b">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>88.28722778104768</v>
+      </c>
+      <c r="V38" t="n">
+        <v>88.28722778104768</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3372,6 +4352,32 @@
       </c>
       <c r="N39" t="b">
         <v>1</v>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T39" t="b">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>67.68350810295519</v>
+      </c>
+      <c r="V39" t="n">
+        <v>67.68350810295519</v>
       </c>
     </row>
     <row r="40">
@@ -3417,6 +4423,28 @@
       <c r="N40" t="b">
         <v>0</v>
       </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T40" t="b">
+        <v>1</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3465,6 +4493,32 @@
       <c r="N41" t="b">
         <v>1</v>
       </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>14.77 for 12, amazon official storefront</t>
+        </is>
+      </c>
+      <c r="T41" t="b">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>224.390243902439</v>
+      </c>
+      <c r="V41" t="n">
+        <v>224.390243902439</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3513,6 +4567,32 @@
       <c r="N42" t="b">
         <v>1</v>
       </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>13.33 for 12, amazon official storefront</t>
+        </is>
+      </c>
+      <c r="T42" t="b">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>278.4810126582279</v>
+      </c>
+      <c r="V42" t="n">
+        <v>278.4810126582279</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3565,6 +4645,32 @@
       <c r="N43" t="b">
         <v>1</v>
       </c>
+      <c r="O43" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T43" t="b">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>-1.716738197424894</v>
+      </c>
+      <c r="V43" t="n">
+        <v>-23.60515021459227</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3616,6 +4722,32 @@
       </c>
       <c r="N44" t="b">
         <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T44" t="b">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>-1.716738197424894</v>
+      </c>
+      <c r="V44" t="n">
+        <v>-23.60515021459227</v>
       </c>
     </row>
     <row r="45">
@@ -3661,6 +4793,24 @@
       <c r="N45" t="b">
         <v>0</v>
       </c>
+      <c r="O45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="b">
+        <v>1</v>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3705,6 +4855,24 @@
       <c r="N46" t="b">
         <v>0</v>
       </c>
+      <c r="O46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="b">
+        <v>1</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3749,6 +4917,28 @@
       <c r="N47" t="b">
         <v>0</v>
       </c>
+      <c r="O47" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T47" t="b">
+        <v>1</v>
+      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3793,6 +4983,28 @@
       <c r="N48" t="b">
         <v>0</v>
       </c>
+      <c r="O48" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T48" t="b">
+        <v>1</v>
+      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3841,6 +5053,32 @@
       <c r="N49" t="b">
         <v>1</v>
       </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T49" t="b">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>-7.147962830593279</v>
+      </c>
+      <c r="V49" t="n">
+        <v>-7.147962830593279</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3889,6 +5127,32 @@
       <c r="N50" t="b">
         <v>1</v>
       </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T50" t="b">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>12.51042535446205</v>
+      </c>
+      <c r="V50" t="n">
+        <v>12.51042535446205</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3937,6 +5201,32 @@
       <c r="N51" t="b">
         <v>1</v>
       </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T51" t="b">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>14.71453796350795</v>
+      </c>
+      <c r="V51" t="n">
+        <v>14.71453796350795</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3988,6 +5278,32 @@
       </c>
       <c r="N52" t="b">
         <v>1</v>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T52" t="b">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>-4.766444232602474</v>
+      </c>
+      <c r="V52" t="n">
+        <v>-4.766444232602474</v>
       </c>
     </row>
     <row r="53">
@@ -4037,6 +5353,28 @@
       <c r="N53" t="b">
         <v>0</v>
       </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T53" t="b">
+        <v>1</v>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4091,6 +5429,32 @@
       <c r="N54" t="b">
         <v>1</v>
       </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>14.77 for 12, amazon official storefront</t>
+        </is>
+      </c>
+      <c r="T54" t="b">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>34.95934959349594</v>
+      </c>
+      <c r="V54" t="n">
+        <v>21.13821138211382</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4145,6 +5509,32 @@
       <c r="N55" t="b">
         <v>1</v>
       </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>13.33 for 12, amazon official storefront</t>
+        </is>
+      </c>
+      <c r="T55" t="b">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>110.126582278481</v>
+      </c>
+      <c r="V55" t="n">
+        <v>88.60759493670885</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4195,6 +5585,32 @@
       <c r="N56" t="b">
         <v>1</v>
       </c>
+      <c r="O56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T56" t="b">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>6.866952789699576</v>
+      </c>
+      <c r="V56" t="n">
+        <v>-27.46781115879828</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4249,6 +5665,28 @@
       <c r="N57" t="b">
         <v>1</v>
       </c>
+      <c r="O57" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+      <c r="T57" t="b">
+        <v>1</v>
+      </c>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4293,6 +5731,24 @@
       <c r="N58" t="b">
         <v>0</v>
       </c>
+      <c r="O58" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="b">
+        <v>1</v>
+      </c>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4337,6 +5793,24 @@
       <c r="N59" t="b">
         <v>0</v>
       </c>
+      <c r="O59" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="b">
+        <v>1</v>
+      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4381,6 +5855,28 @@
       <c r="N60" t="b">
         <v>0</v>
       </c>
+      <c r="O60" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T60" t="b">
+        <v>1</v>
+      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4430,6 +5926,32 @@
       </c>
       <c r="N61" t="b">
         <v>1</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+      <c r="T61" t="b">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>30.65693430656933</v>
+      </c>
+      <c r="V61" t="n">
+        <v>9.48905109489051</v>
       </c>
     </row>
     <row r="62">
@@ -4475,6 +5997,28 @@
       <c r="N62" t="b">
         <v>0</v>
       </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T62" t="b">
+        <v>1</v>
+      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4519,6 +6063,28 @@
       <c r="N63" t="b">
         <v>0</v>
       </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T63" t="b">
+        <v>1</v>
+      </c>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4571,6 +6137,32 @@
       <c r="N64" t="b">
         <v>1</v>
       </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T64" t="b">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>23.54326074161273</v>
+      </c>
+      <c r="V64" t="n">
+        <v>23.54326074161273</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4623,6 +6215,32 @@
       <c r="N65" t="b">
         <v>1</v>
       </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T65" t="b">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4674,6 +6292,32 @@
       </c>
       <c r="N66" t="b">
         <v>1</v>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+      <c r="T66" t="b">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>-7.168458781362008</v>
+      </c>
+      <c r="V66" t="n">
+        <v>-7.168458781362008</v>
       </c>
     </row>
     <row r="67">
@@ -4727,6 +6371,28 @@
       <c r="N67" t="b">
         <v>1</v>
       </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>14.77 for 12, amazon official storefront</t>
+        </is>
+      </c>
+      <c r="T67" t="b">
+        <v>1</v>
+      </c>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4779,6 +6445,518 @@
       <c r="N68" t="b">
         <v>1</v>
       </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>13.33 for 12, amazon official storefront</t>
+        </is>
+      </c>
+      <c r="T68" t="b">
+        <v>1</v>
+      </c>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>storefront_price</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>amazon_total_wine_price</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>control_price</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>control_source</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>control_note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RXBAR | Bluberry</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RXBAR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bluberry</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RXBAR | Peanut Butter</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RXBAR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Peanut Butter</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>27.99 for 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Big Spoon | Cherry chocolate</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Big Spoon</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cherry chocolate</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Big Spoon | Apricot pepita</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Big Spoon</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apricot pepita</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Luna | Bluberry, 1.69 oz</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Luna</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bluberry, 1.69 oz</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Luna | Lemon zest, 1.69</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Luna</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lemon zest, 1.69</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>storefront</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>20.57 for 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kind | Dark chocolate mocha almond, 12 oz bar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Dark chocolate mocha almond, 12 oz bar</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>14.77 for 12, amazon official storefront</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kind | Peanut butter dark chocolate, 12 oz bar</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Peanut butter dark chocolate, 12 oz bar</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>13.33 for 12, amazon official storefront</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Pisgah | 6 pack pale ale</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pisgah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6 pack pale ale</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="F10" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ponysaurus | Biere de garde, 6 pk</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ponysaurus</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Biere de garde, 6 pk</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sierra Nevada | Pale ale 12 pk</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sierra Nevada</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pale ale 12 pk</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F12" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Blue Ribbon | Narragansett, 12 pk lager cans</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Blue Ribbon</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Narragansett, 12 pk lager cans</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Budweiser | 25 oz bud light</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Budweiser</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>25 oz bud light</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Amazon / Total Wine</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>no official seller</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/clean/price_table.xlsx
+++ b/data/clean/price_table.xlsx
@@ -21,13 +21,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,64 +454,64 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Bulldega</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Durham Co-op</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Food Lion</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Gazelle</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Harris Teeter</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Whole Foods</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>n_stores</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>control_price</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>beer</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Blue Ribbon | Narragansett, 12 pk lager cans</t>
         </is>
@@ -507,7 +540,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Budweiser | 25 oz bud light</t>
         </is>
@@ -532,7 +566,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Pisgah | 6 pack pale ale</t>
         </is>
@@ -555,7 +590,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Ponysaurus | Biere de garde, 6 pk</t>
         </is>
@@ -580,7 +616,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>Sierra Nevada | Pale ale 12 pk</t>
         </is>
@@ -609,12 +646,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>Organic Valley | Organic 2%, 64 fz</t>
         </is>
@@ -633,12 +670,12 @@
       <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>pantry</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>Annie's | Classic cheddar pasta, 6 oz</t>
         </is>
@@ -657,7 +694,8 @@
       <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>Annie's | Organic classic cheddar pasta, 6 oz</t>
         </is>
@@ -676,7 +714,8 @@
       <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>Jovial | Gf elbows</t>
         </is>
@@ -695,7 +734,8 @@
       <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>Jovial | Gf penne</t>
         </is>
@@ -714,12 +754,12 @@
       <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>snack</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>Kettle brand | Sour cream and onion, 5 oz</t>
         </is>
@@ -738,12 +778,12 @@
       <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>snack bar</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>Big Spoon | Apricot pepita</t>
         </is>
@@ -766,7 +806,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>Big Spoon | Cherry chocolate</t>
         </is>
@@ -789,7 +830,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>Hu chocolate | Almond butter + puffed quinoa dark chocolate</t>
         </is>
@@ -808,7 +850,8 @@
       <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>Kind | Dark chocolate mocha almond, 12 oz bar</t>
         </is>
@@ -835,7 +878,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>Kind | Peanut butter dark chocolate, 12 oz bar</t>
         </is>
@@ -862,7 +906,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>Luna | Bluberry, 1.69 oz</t>
         </is>
@@ -885,7 +930,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>Luna | Lemon zest, 1.69</t>
         </is>
@@ -910,7 +956,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>RXBAR | Bluberry</t>
         </is>
@@ -937,7 +984,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>RXBAR | Peanut butter</t>
         </is>
@@ -983,59 +1031,59 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Bulldega</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Durham Co-op</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Food Lion</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Gazelle</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Harris Teeter</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Whole Foods</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>control_price</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>beer</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Blue Ribbon | Narragansett, 12 pk lager cans</t>
         </is>
@@ -1061,7 +1109,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Budweiser | 25 oz bud light</t>
         </is>
@@ -1083,7 +1132,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Pisgah | 6 pack pale ale</t>
         </is>
@@ -1103,7 +1153,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Ponysaurus | Biere de garde, 6 pk</t>
         </is>
@@ -1125,7 +1176,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>Sierra Nevada | Pale ale 12 pk</t>
         </is>
@@ -1151,12 +1203,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>Organic Valley | Organic 2%, 64 fz</t>
         </is>
@@ -1172,12 +1224,12 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>pantry</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>Annie's | Classic cheddar pasta, 6 oz</t>
         </is>
@@ -1193,7 +1245,8 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>Annie's | Organic classic cheddar pasta, 6 oz</t>
         </is>
@@ -1209,7 +1262,8 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>Jovial | Gf elbows</t>
         </is>
@@ -1225,7 +1279,8 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>Jovial | Gf penne</t>
         </is>
@@ -1241,12 +1296,12 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>snack</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>Kettle brand | Sour cream and onion, 5 oz</t>
         </is>
@@ -1262,12 +1317,12 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>snack bar</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>Big Spoon | Apricot pepita</t>
         </is>
@@ -1287,7 +1342,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>Big Spoon | Cherry chocolate</t>
         </is>
@@ -1307,7 +1363,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>Hu chocolate | Almond butter + puffed quinoa dark chocolate</t>
         </is>
@@ -1323,7 +1380,8 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>Kind | Dark chocolate mocha almond, 12 oz bar</t>
         </is>
@@ -1347,7 +1405,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>Kind | Peanut butter dark chocolate, 12 oz bar</t>
         </is>
@@ -1371,7 +1430,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>Luna | Bluberry, 1.69 oz</t>
         </is>
@@ -1391,7 +1451,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>Luna | Lemon zest, 1.69</t>
         </is>
@@ -1413,7 +1474,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>RXBAR | Bluberry</t>
         </is>
@@ -1437,7 +1499,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>RXBAR | Peanut butter</t>
         </is>
@@ -1480,22 +1543,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>store</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>regular_price</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1634,112 +1697,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>store</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>store_type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>regular_price</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sale_price</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>member_price</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>shelf</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>substitute</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>paid_price</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>found</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>storefront_price</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>amazon_total_wine_price</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>control_price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>control_source</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>control_note</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>has_control</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>regular_premium_pct</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>paid_premium_pct</t>
         </is>
@@ -7572,42 +7635,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>storefront_price</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>amazon_total_wine_price</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>control_price</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>control_source</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>control_note</t>
         </is>
